--- a/output/pdf_financials_xlsx/WEST.xlsx
+++ b/output/pdf_financials_xlsx/WEST.xlsx
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.707872</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.913014</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.950514</v>
       </c>
     </row>
     <row r="93">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.152549</v>
+        <v>0.023542</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>4.438459</v>
+        <v>4.310934</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.687885</v>
+        <v>0.665351</v>
       </c>
     </row>
     <row r="119">
@@ -3101,7 +3101,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>3.707872</v>
       </c>
@@ -3620,7 +3624,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4178,7 +4186,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>-0.129007</v>
       </c>

--- a/output/pdf_financials_xlsx/WEST.xlsx
+++ b/output/pdf_financials_xlsx/WEST.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001011</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004743</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001161</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.129922</v>
+        <v>-1.130933</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.136994</v>
+        <v>-5.141737</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.344184</v>
+        <v>-1.345345</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.129922</v>
+        <v>-1.130933</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.136994</v>
+        <v>-5.141737</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.344184</v>
+        <v>-1.345345</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003157</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.049626</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001217</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.018</v>
+        <v>0.021157</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.052376</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001217</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.02297</v>
+        <v>0.019813</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.077607</v>
+        <v>0.027981</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.028615</v>
+        <v>0.027398</v>
       </c>
     </row>
     <row r="49">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">

--- a/output/pdf_financials_xlsx/WEST.xlsx
+++ b/output/pdf_financials_xlsx/WEST.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.764213</v>
+        <v>0.817712</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.327165</v>
+        <v>1.43815</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.412465</v>
+        <v>0.507672</v>
       </c>
     </row>
     <row r="8">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="116">
@@ -3688,7 +3688,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3752,7 +3756,11 @@
           <t>Issuance of shares – private placement</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -4599,7 +4607,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.053499</v>
       </c>
